--- a/dq-lab-1/DSAI-DQ-Lab-2-Answer-Sheet.xlsx
+++ b/dq-lab-1/DSAI-DQ-Lab-2-Answer-Sheet.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m.vankeulen/Documents/Onderwijs/DSAI module/Repository/dsai/DQ/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91DBC13-70C5-FE4E-8116-E183EFC36F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="26380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="26380" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Answers" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Answers" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>Exercise</t>
   </si>
@@ -32,48 +26,94 @@
     <t>1(a)</t>
   </si>
   <si>
+    <t>a, c, d, e</t>
+  </si>
+  <si>
     <t>1(b)</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>1(c)</t>
   </si>
   <si>
+    <t>b</t>
+  </si>
+  <si>
     <t>1(d)</t>
   </si>
   <si>
+    <t>d</t>
+  </si>
+  <si>
     <t>1(e)</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>1(f)</t>
   </si>
   <si>
+    <t>Mary Lawson, Peter Blanks, Floor Dessing</t>
+  </si>
+  <si>
     <t>1(g)</t>
   </si>
   <si>
+    <t>Mary Lawson only under the update-repair (attribute-based) interpretation of CQA. Reasoning with tuple-deletion repairs (each violation resolved by deleting one conflicting tuple): the cid FD (John/Jon Lawson), the rid FD (plane A380/A300 for rid=1) and the tcode FD (Vienna/Wenen for VIE) together yield three maximal consistent repairs, and their query results intersect to the empty set (no name is certain under strict tuple-deletion CQA). If instead violations are repaired by correcting the deviating attribute value (keeping the majority/uncorrupted value), Mary Lawson survives in every repair and is the certain answer.</t>
+  </si>
+  <si>
     <t>2(a)</t>
   </si>
   <si>
+    <t>Three violations, all for FD album,year -&gt; genre: (1) row "Billie Jean" (Thriller,1982,Pop) vs row "Beat It" (Thriller,1982,Rock); (2) row "Beat It" (Thriller,1982,Rock) vs row "Human Nature" (Thriller,1982,Pop); (3) row "Starboy" (Starboy,2016,Pop) vs row "I Feel It Coming" (Starboy,2016,R&amp;B). "Beat It" is involved in two of the three violations.</t>
+  </si>
+  <si>
     <t>2(b)</t>
   </si>
   <si>
+    <t>64</t>
+  </si>
+  <si>
     <t>2(c)</t>
   </si>
   <si>
+    <t>One update can fix multiple violations simultaneously: updating row "Beat It" genre from Rock to Pop resolves both violation 1 (vs "Billie Jean") and violation 2 (vs "Human Nature") at once, because "Beat It" is the shared row in both violations. Combined with one more update (e.g. fixing "Starboy" or "I Feel It Coming"), only 2 update-repairs (cost 2) are needed to solve all 3 violations.</t>
+  </si>
+  <si>
     <t>3(a)</t>
   </si>
   <si>
+    <t>0.75</t>
+  </si>
+  <si>
     <t>3(b)</t>
   </si>
   <si>
     <t>3(c)</t>
   </si>
   <si>
+    <t xml:space="preserve">4 possible partitionings. A-B=0.95 &gt;= Tµ so A,B always merge definitely. D-E=0.45 and A-C=0.45 (and B-C=0.50) fall in the gray zone [Tλ,Tµ), so C-joins-{A,B} and D-E-merge are each an independent free choice:
+1) {A,B,C}, {D}, {E}
+2) {A,B,C}, {D,E}
+3) {A,B}, {C}, {D}, {E}
+4) {A,B}, {C}, {D,E}</t>
+  </si>
+  <si>
     <t>3(d)</t>
   </si>
   <si>
+    <t>Depends on the probability formula taught; under the standard linear-interpolation assumption p = (score - Tλ)/(Tµ - Tλ) for gray-zone pairs, treated as independent: A-C=0.45 -&gt; p(merge)=0.1, D-E=0.45 -&gt; p(merge)=0.1. Example for partitioning {A,B,C},{D},{E}: P = p(A-C merge) x p(D-E not merge) = 0.1 x 0.9 = 0.09.</t>
+  </si>
+  <si>
     <t>3(e)</t>
   </si>
   <si>
+    <t>They do not have to remain as two separate alternatives forever. A probabilistic database can store both partitionings as uncertain/alternative worlds (with their probabilities), but the uncertainty can get resolved later, e.g. when more evidence/data arrives (new records, user feedback, additional attributes) that makes one partitioning much more likely than the other, or when a query result depends on it and the answer must be materialized. Until resolved, both alternatives coexist as possible worlds with associated probabilities.</t>
+  </si>
+  <si>
     <t>4(a)</t>
   </si>
   <si>
@@ -83,12 +123,21 @@
     <t>4(c)</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>5(a)</t>
   </si>
   <si>
+    <t>Yes, quality depends on context/use</t>
+  </si>
+  <si>
     <t>5(b)</t>
   </si>
   <si>
+    <t>Yes, correctness alone doesn't guarantee fitness for use</t>
+  </si>
+  <si>
     <t>5(c)</t>
   </si>
   <si>
@@ -98,7 +147,13 @@
     <t>5(e)</t>
   </si>
   <si>
+    <t>A huge rule system (e.g. thousands of if-then rules or a massive decision tree) is traceable: every decision path can be printed out step by step. But a human cannot hold thousands of interacting rules in their head, so it is not interpretable in practice, even though it is fully traceable.</t>
+  </si>
+  <si>
     <t>5(f)</t>
+  </si>
+  <si>
+    <t>Removing the 8% can cause selection bias if the missingness isn't random: if patients missing a picture differ systematically (e.g. specific view was skipped because that breast looked suspicious, or due to a machine/procedure differences), then the model trained only on complete cases would be trained on a biased, non-representative subset, harming generalization and potentially missing exactly the harder/riskier cases.</t>
   </si>
   <si>
     <t>Instructions</t>
@@ -125,19 +180,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -154,20 +216,16 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -181,13 +239,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor theme="6" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -231,42 +289,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -562,216 +619,276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="26" style="11" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="20" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="9"/>
-    </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="9"/>
-    </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="9"/>
-    </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-    </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="9"/>
-    </row>
-    <row r="14" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="B10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="B12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="B13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
+      <c r="B14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" ht="75" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." sqref="B2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." sqref="B18">
+      <formula1>"a,b,c,d"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." sqref="B2">
       <formula1>"a,b,c,d,e,f"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." sqref="B3 B18 B5" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." sqref="B23">
+      <formula1>"a,b,c"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." sqref="B3">
       <formula1>"a,b,c,d"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." sqref="B4 B23" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." sqref="B4">
       <formula1>"a,b,c"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" promptTitle="Multiple choice" prompt="Select the letter(s) of the correct choice(s) as shown in the PDF." errorTitle="Invalid answer" error="Please pick a letter matching the choice(s) in the PDF." sqref="B5">
+      <formula1>"a,b,c,d"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -779,55 +896,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
-    <col min="1" max="1" width="90" customWidth="1"/>
+    <col min="1" max="1" width="90" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5"/>
-    </row>
-    <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-    </row>
-    <row r="6" spans="1:1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-    </row>
-    <row r="10" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>32</v>
+    <row r="1" ht="20" customHeight="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+    </row>
+    <row r="10" ht="16" customHeight="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
